--- a/data/trans_camb/IP16A02-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.346728687425682</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.969205384492654</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.07179400145028852</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.931699528933991</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.25959431295782</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.958975023057275</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-5.872718303147171</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.847234768553439</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.51135398115097</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.588351749666106</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.616664332837134</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-0.7101993436744581</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.584701064208903</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.122085066223763</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.35237721389113</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.601088244200042</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.119174941476345</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>7.515115348608874</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.3744104860943158</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.4737239704267947</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.01206653429061305</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.4927354957384668</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2060549808799615</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.4840539017428604</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.6783411012420412</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.2681672889444912</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.4557980639316703</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3744562693435093</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4738312191318042</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1214708886967463</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1939958166931534</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1.904454140249683</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.8112871070877495</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.11404959241072</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2533751412487073</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.491457261823521</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.02029394914484575</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.291460579713077</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.011517183800829</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.779122274149255</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.4945039984489363</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>7.044321828987407</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-3.283023478330654</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2.732730894092571</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.148211537110572</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2.321084070933503</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.001161156640789</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>3.42177989610086</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.770780789598422</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.20245360426342</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.263332305517438</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.48973069363202</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.177130276283235</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10.56255148976495</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.004025717382148874</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1.446409438966166</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.1932408040450165</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.295087280725847</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.09624693088492459</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.371059401607099</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5067739534472425</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.3966296681502233</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.601623708902674</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.3194181793892659</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4732237203226532</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.4904282738336411</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.137901351182618</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>3.667692240705214</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.7166911024605918</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3.705706725438559</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5353773256365636</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.685227008838455</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-2.742766475865963</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.551407841261148</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.911912133016955</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.558173989578999</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-2.840579675279361</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.932084061674194</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-6.394699222406344</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.508741682813537</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.359899266212148</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.305720422403246</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.448017687204485</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.7523401894556104</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0.7680295690530775</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.914170704712832</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3255947194913069</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10.17551754424359</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.6759088197231278</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>7.261201751193255</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.5178801215268114</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.4817484151579499</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.6227968756656764</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1.188776733977046</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.5691627472845211</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.7878658664541994</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.8513416565181123</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.2482368735226499</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.9159938357226753</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.1003020642921597</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8189278424755981</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.06301175900429284</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.3056192847459339</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.145822592292179</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.4208810222635313</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3.728811164667366</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.1078038869784693</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.12222543396599</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.6038504016713769</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>7.93678515414466</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-3.149875138946266</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>6.75499306385696</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.740022994887958</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>7.400795989675396</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.559365431497683</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2.120281524504721</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.437169207788406</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.00350395287933962</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-5.339246870073511</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>2.797301532067693</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>4.112161358727972</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>14.25750665945168</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.546315334212722</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>12.97374750120125</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.807551970247139</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>11.50080052713109</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.1298935385496941</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.707272373301456</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.5375663724269399</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1.152825733378593</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.3346828878923438</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1.423498299622258</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.7754188844780506</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.1324341380751929</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.9260924963037055</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.09599573080134202</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.7210238356867605</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.3263033765455658</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>1.909782806696883</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>6.465723012646113</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.9256543522149141</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>4.871764299399957</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.7179400883172599</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>3.694282065633564</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.500526825078234</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>4.959937627706047</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.307163354985717</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>5.724343876552368</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.406602789760405</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>5.318697100002796</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.325594967977315</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2.512677621005813</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.187539574726043</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>3.407296240350227</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.517671085457245</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>3.688417955007131</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.2700555207846119</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>7.350038221497028</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.4039216816491257</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>8.375869290979447</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.03801581463143748</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>7.345376847296746</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.2742181203793065</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.9064181664311375</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.2406865096855148</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1.054016961714853</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.2579985166743309</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.9755532780327588</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.5129446324149838</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.3933945528982009</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.4926396411064419</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.5269171935402857</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.4177616812060613</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.5866479616860359</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.06999161241088198</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.644129231321013</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.1061385790081778</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.884786453790232</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.006207985137629038</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1.522984051696736</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
